--- a/output/upload/S00027_1758_스마트V연금보험_무배당.xlsx
+++ b/output/upload/S00027_1758_스마트V연금보험_무배당.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3814,8 +4250,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3859,8 +4318,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3904,8 +4386,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3949,8 +4454,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -3994,8 +4522,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4039,8 +4590,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4084,8 +4658,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4129,8 +4726,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4174,8 +4794,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4219,8 +4862,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4264,8 +4930,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4309,8 +4998,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4354,8 +5066,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4399,8 +5134,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4444,8 +5202,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4489,8 +5270,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4534,8 +5338,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4579,8 +5406,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4624,8 +5474,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4669,8 +5542,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4714,8 +5610,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4759,8 +5678,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4804,8 +5746,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4849,8 +5814,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4894,8 +5882,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4939,8 +5950,31 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -4984,8 +6018,31 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5029,8 +6086,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5074,8 +6154,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5119,8 +6222,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5164,8 +6290,31 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5209,8 +6358,31 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5254,8 +6426,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5299,8 +6494,31 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5344,8 +6562,31 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5389,8 +6630,31 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5434,8 +6698,31 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5479,8 +6766,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5524,8 +6834,31 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5569,8 +6902,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5614,8 +6970,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5659,8 +7038,31 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260101</t>
@@ -5704,8 +7106,31 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1758232</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260101</t>

--- a/output/upload/S00027_1758_스마트V연금보험_무배당.xlsx
+++ b/output/upload/S00027_1758_스마트V연금보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW69"/>
+  <dimension ref="A1:AW27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
@@ -2658,11 +2658,11 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L7" s="6" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -2751,21 +2751,21 @@
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J8" s="6" t="inlineStr">
+        <is>
           <t>N5</t>
         </is>
       </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L8" s="6" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
@@ -2864,11 +2864,11 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L9" s="6" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -2957,7 +2957,7 @@
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
@@ -2967,11 +2967,11 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L10" s="6" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
@@ -3070,11 +3070,11 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L11" s="6" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
@@ -3173,11 +3173,11 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L12" s="6" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
@@ -3276,11 +3276,11 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L13" s="6" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -3369,21 +3369,21 @@
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
           <t>N3</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L14" s="6" t="n">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3481,11 +3481,11 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -3549,11 +3549,11 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -3617,11 +3617,11 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -3675,7 +3675,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -3685,11 +3685,11 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -3753,11 +3753,11 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>A999</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3821,11 +3821,11 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3</v>
+        <v>999</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -4312,2862 +4312,6 @@
         <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>5</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>5</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>5</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>7</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>5</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>10</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>5</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>15</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>5</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>20</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>5</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>3</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>3</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>3</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>7</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>3</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>10</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>3</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>15</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>3</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>20</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>3</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>999</v>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N42" t="n">
-        <v>3</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>999</v>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N43" t="n">
-        <v>5</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>999</v>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>7</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>999</v>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>10</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>999</v>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N46" t="n">
-        <v>15</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>999</v>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N47" t="n">
-        <v>20</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L48" t="n">
-        <v>999</v>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L49" t="n">
-        <v>5</v>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N49" t="n">
-        <v>3</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L50" t="n">
-        <v>5</v>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N50" t="n">
-        <v>5</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L51" t="n">
-        <v>5</v>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N51" t="n">
-        <v>7</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L52" t="n">
-        <v>5</v>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N52" t="n">
-        <v>10</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L53" t="n">
-        <v>5</v>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N53" t="n">
-        <v>15</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>5</v>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N54" t="n">
-        <v>20</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>5</v>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>3</v>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N56" t="n">
-        <v>3</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L57" t="n">
-        <v>3</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N57" t="n">
-        <v>5</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L58" t="n">
-        <v>3</v>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N58" t="n">
-        <v>7</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L59" t="n">
-        <v>3</v>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N59" t="n">
-        <v>10</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L60" t="n">
-        <v>3</v>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N60" t="n">
-        <v>15</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L61" t="n">
-        <v>3</v>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N61" t="n">
-        <v>20</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>3</v>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N62" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>999</v>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N63" t="n">
-        <v>3</v>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L64" t="n">
-        <v>999</v>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N64" t="n">
-        <v>5</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>999</v>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N65" t="n">
-        <v>7</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>999</v>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N66" t="n">
-        <v>10</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>999</v>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N67" t="n">
-        <v>15</v>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>999</v>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N68" t="n">
-        <v>20</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>1758232</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>999</v>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N69" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_1758_스마트V연금보험_무배당.xlsx
+++ b/output/upload/S00027_1758_스마트V연금보험_무배당.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW27"/>
+  <dimension ref="A1:AW41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3334,22 +3334,22 @@
       <c r="A14" s="5" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -3436,22 +3436,22 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3504,22 +3504,22 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3572,22 +3572,22 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3640,22 +3640,22 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3708,22 +3708,22 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3776,22 +3776,22 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3844,22 +3844,22 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3912,22 +3912,22 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3980,22 +3980,22 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4048,22 +4048,22 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4116,22 +4116,22 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4184,22 +4184,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4252,22 +4252,22 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4312,6 +4312,958 @@
         <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>999</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>999</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>999</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>7</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>999</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>999</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>15</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>999</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>20</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1758235</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>999</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>N3</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>999</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>3</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>N5</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>999</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>N7</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>999</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>7</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>999</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>999</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>15</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>999</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>20</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1758236</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>20260101</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>N0</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>999</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_1758_스마트V연금보험_무배당.xlsx
+++ b/output/upload/S00027_1758_스마트V연금보험_무배당.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW41"/>
+  <dimension ref="A1:AW22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -2685,9 +2685,17 @@
       <c r="U7" s="6" t="n"/>
       <c r="V7" s="6" t="n"/>
       <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
+      <c r="X7" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y7" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z7" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA7" s="6" t="n"/>
       <c r="AB7" s="6" t="n"/>
       <c r="AC7" s="6" t="n"/>
@@ -2788,9 +2796,17 @@
       <c r="U8" s="6" t="n"/>
       <c r="V8" s="6" t="n"/>
       <c r="W8" s="6" t="n"/>
-      <c r="X8" s="6" t="n"/>
-      <c r="Y8" s="6" t="n"/>
-      <c r="Z8" s="6" t="n"/>
+      <c r="X8" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y8" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z8" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA8" s="6" t="n"/>
       <c r="AB8" s="6" t="n"/>
       <c r="AC8" s="6" t="n"/>
@@ -2891,9 +2907,17 @@
       <c r="U9" s="6" t="n"/>
       <c r="V9" s="6" t="n"/>
       <c r="W9" s="6" t="n"/>
-      <c r="X9" s="6" t="n"/>
-      <c r="Y9" s="6" t="n"/>
-      <c r="Z9" s="6" t="n"/>
+      <c r="X9" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y9" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z9" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA9" s="6" t="n"/>
       <c r="AB9" s="6" t="n"/>
       <c r="AC9" s="6" t="n"/>
@@ -2994,9 +3018,17 @@
       <c r="U10" s="6" t="n"/>
       <c r="V10" s="6" t="n"/>
       <c r="W10" s="6" t="n"/>
-      <c r="X10" s="6" t="n"/>
-      <c r="Y10" s="6" t="n"/>
-      <c r="Z10" s="6" t="n"/>
+      <c r="X10" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y10" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z10" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA10" s="6" t="n"/>
       <c r="AB10" s="6" t="n"/>
       <c r="AC10" s="6" t="n"/>
@@ -3097,9 +3129,17 @@
       <c r="U11" s="6" t="n"/>
       <c r="V11" s="6" t="n"/>
       <c r="W11" s="6" t="n"/>
-      <c r="X11" s="6" t="n"/>
-      <c r="Y11" s="6" t="n"/>
-      <c r="Z11" s="6" t="n"/>
+      <c r="X11" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y11" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z11" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA11" s="6" t="n"/>
       <c r="AB11" s="6" t="n"/>
       <c r="AC11" s="6" t="n"/>
@@ -3200,9 +3240,17 @@
       <c r="U12" s="6" t="n"/>
       <c r="V12" s="6" t="n"/>
       <c r="W12" s="6" t="n"/>
-      <c r="X12" s="6" t="n"/>
-      <c r="Y12" s="6" t="n"/>
-      <c r="Z12" s="6" t="n"/>
+      <c r="X12" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y12" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z12" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA12" s="6" t="n"/>
       <c r="AB12" s="6" t="n"/>
       <c r="AC12" s="6" t="n"/>
@@ -3231,22 +3279,22 @@
       <c r="A13" s="5" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1758232</t>
+          <t>1758233</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 1종(기본형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -3271,7 +3319,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -3288,7 +3336,7 @@
         </is>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" s="6" t="inlineStr">
         <is>
@@ -3303,9 +3351,17 @@
       <c r="U13" s="6" t="n"/>
       <c r="V13" s="6" t="n"/>
       <c r="W13" s="6" t="n"/>
-      <c r="X13" s="6" t="n"/>
-      <c r="Y13" s="6" t="n"/>
-      <c r="Z13" s="6" t="n"/>
+      <c r="X13" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y13" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z13" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA13" s="6" t="n"/>
       <c r="AB13" s="6" t="n"/>
       <c r="AC13" s="6" t="n"/>
@@ -3374,7 +3430,7 @@
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -3391,7 +3447,7 @@
         </is>
       </c>
       <c r="N14" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
@@ -3406,9 +3462,17 @@
       <c r="U14" s="6" t="n"/>
       <c r="V14" s="6" t="n"/>
       <c r="W14" s="6" t="n"/>
-      <c r="X14" s="6" t="n"/>
-      <c r="Y14" s="6" t="n"/>
-      <c r="Z14" s="6" t="n"/>
+      <c r="X14" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y14" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z14" s="6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
       <c r="AA14" s="6" t="n"/>
       <c r="AB14" s="6" t="n"/>
       <c r="AC14" s="6" t="n"/>
@@ -3476,7 +3540,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3493,11 +3557,22 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -3544,7 +3619,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>N7</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3561,11 +3636,22 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3698,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -3629,11 +3715,22 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3777,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -3697,33 +3794,44 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>1758233</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1758233</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3748,7 +3856,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>N20</t>
+          <t>N3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -3765,33 +3873,44 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>1758233</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1758233</t>
+          <t>1758234</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3816,7 +3935,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>N0</t>
+          <t>N5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -3833,33 +3952,44 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>1758234</t>
+          <t>1758235</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1758234</t>
+          <t>1758235</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3884,7 +4014,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>N3</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3901,7 +4031,7 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -3912,22 +4042,22 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>1758234</t>
+          <t>1758236</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1758234</t>
+          <t>1758236</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
+          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3952,7 +4082,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>N5</t>
+          <t>N0</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3969,1301 +4099,9 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L23" t="n">
-        <v>999</v>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>7</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>999</v>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>10</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>999</v>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>15</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>999</v>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
-        <v>20</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>1758234</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 적립형 3종(연금강화형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>999</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>999</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N28" t="n">
-        <v>3</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>999</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
-        <v>5</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>999</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>7</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>999</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N31" t="n">
-        <v>10</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>999</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>15</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>999</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N33" t="n">
-        <v>20</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>1758235</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 1종(기본형)(종신연금형) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>999</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N34" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N3</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>999</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N35" t="n">
-        <v>3</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>N5</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>999</v>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N36" t="n">
-        <v>5</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>N7</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>999</v>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N37" t="n">
-        <v>7</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N10</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>999</v>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N38" t="n">
-        <v>10</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N15</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>999</v>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>15</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>999</v>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N40" t="n">
-        <v>20</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>1,2,3,4,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>1758236</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>한화생명 스마트V연금보험 무배당 거치형 2종(가족사랑형)(가족종신연금,가족사랑연금) 가산할인형</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>S00027</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>20260101</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>99991231</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>A999</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>N0</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>999</v>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="N41" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>
